--- a/tests/SafeOpenXml.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Raa891a67b91f4bc2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfd1ecf1cec0a40dc"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfd1ecf1cec0a40dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R02b1b8b0a0cf4d72"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R02b1b8b0a0cf4d72"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rabbe7039851e4101"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rabbe7039851e4101"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R296f4f7048294126"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R296f4f7048294126"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R45ada06b4a5146e3"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R45ada06b4a5146e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R965915f42d194916"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R965915f42d194916"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R223527dad126402c"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R223527dad126402c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd07dbd6ae98b4f50"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd07dbd6ae98b4f50"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbb73be2762d14a1a"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbb73be2762d14a1a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc3c4f793a40d43bf"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc3c4f793a40d43bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5514f1bb2d924f6d"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5514f1bb2d924f6d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rddc1a7ccf5b746d5"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rddc1a7ccf5b746d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rcb4201be48344185"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rcb4201be48344185"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0a4de03756344a47"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0a4de03756344a47"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7cb8fec3654c4a08"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7cb8fec3654c4a08"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rcbc6f8bdda3748e2"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rcbc6f8bdda3748e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8c046c87e6b749a0"/>
   </x:sheets>
 </x:workbook>
 </file>
